--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-nationality.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T16:21:35+00:00</t>
+    <t>2023-05-26T16:24:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-nationality.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T16:24:55+00:00</t>
+    <t>2023-05-26T18:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-nationality.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T18:19:44+00:00</t>
+    <t>2023-05-30T15:17:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-nationality.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:17:13+00:00</t>
+    <t>2023-05-30T15:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-nationality.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:28:39+00:00</t>
+    <t>2023-05-30T15:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-nationality.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:33:40+00:00</t>
+    <t>2023-05-30T15:59:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-nationality.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:59:25+00:00</t>
+    <t>2023-05-30T16:40:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-nationality.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T16:40:03+00:00</t>
+    <t>2023-05-30T16:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-nationality.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T16:54:18+00:00</t>
+    <t>2023-05-30T17:00:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-nationality.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T17:00:44+00:00</t>
+    <t>2023-05-30T17:09:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-nationality.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-nationality.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="136">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitioner-nationality</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitioner-nationality</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T17:09:40+00:00</t>
+    <t>2023-06-08T09:23:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -387,11 +387,13 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Liste des pays (codes INSEE)</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J74-Pays-RASS/FHIR/JDV-J74-Pays-RASS</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -399,21 +401,6 @@
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
-  </si>
-  <si>
-    <t>Extension.extension:code.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Liste des pays (codes INSEE)</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J74-Pays-RASS/FHIR/JDV-J74-Pays-RASS</t>
   </si>
   <si>
     <t>Extension.extension:period</t>
@@ -747,12 +734,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK17"/>
+  <dimension ref="A1:AK16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="54.56640625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="35.60546875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="29.1484375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="12.64453125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1691,29 +1678,31 @@
         <v>74</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="AA9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>75</v>
@@ -1725,7 +1714,7 @@
         <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>99</v>
@@ -1733,13 +1722,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>74</v>
@@ -1761,15 +1750,17 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N10" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>129</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>74</v>
@@ -1794,13 +1785,13 @@
         <v>74</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>129</v>
+        <v>74</v>
       </c>
       <c r="AA10" t="s" s="2">
         <v>74</v>
@@ -1818,22 +1809,22 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>99</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11">
@@ -1841,11 +1832,9 @@
         <v>130</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>131</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>74</v>
       </c>
@@ -1866,17 +1855,15 @@
         <v>74</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>133</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>74</v>
@@ -1925,30 +1912,30 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>74</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1959,7 +1946,7 @@
         <v>75</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>
@@ -1971,13 +1958,13 @@
         <v>74</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2016,42 +2003,42 @@
         <v>74</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2059,10 +2046,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>74</v>
@@ -2074,22 +2061,24 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2119,42 +2108,42 @@
         <v>74</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>74</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2162,7 +2151,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>82</v>
@@ -2177,24 +2166,22 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="S14" t="s" s="2">
         <v>74</v>
@@ -2236,19 +2223,19 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>99</v>
@@ -2256,10 +2243,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2267,7 +2254,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>82</v>
@@ -2282,22 +2269,24 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="S15" t="s" s="2">
         <v>74</v>
@@ -2339,19 +2328,19 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>99</v>
@@ -2359,10 +2348,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2370,10 +2359,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>74</v>
@@ -2385,24 +2374,22 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="S16" t="s" s="2">
         <v>74</v>
@@ -2444,124 +2431,21 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E17" s="2"/>
-      <c r="F17" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G17" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K17" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q17" s="2"/>
-      <c r="R17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AK17" t="s" s="2">
         <v>99</v>
       </c>
     </row>
